--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.6517101391485</v>
+        <v>2.055902897611631</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0906432007326</v>
+        <v>1.964729520119048</v>
       </c>
       <c r="E2" t="n">
-        <v>17.26769115768437</v>
+        <v>2.805999813123711</v>
       </c>
       <c r="F2" t="n">
-        <v>16.42701074371571</v>
+        <v>2.669389245853803</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.04270566220873</v>
+        <v>4.719439670108919</v>
       </c>
       <c r="D3" t="n">
-        <v>28.00232879941614</v>
+        <v>4.550378429905123</v>
       </c>
       <c r="E3" t="n">
-        <v>17.26769115768437</v>
+        <v>2.805999813123711</v>
       </c>
       <c r="F3" t="n">
-        <v>16.42701074371571</v>
+        <v>2.669389245853803</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.61524989232412</v>
+        <v>8.87497810750267</v>
       </c>
       <c r="D4" t="n">
-        <v>52.05310664237534</v>
+        <v>8.458629829385993</v>
       </c>
       <c r="E4" t="n">
-        <v>17.26769115768437</v>
+        <v>2.805999813123711</v>
       </c>
       <c r="F4" t="n">
-        <v>16.42701074371571</v>
+        <v>2.669389245853803</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
